--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Verde pubblico.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Verde pubblico.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
   <si>
     <r>
       <t xml:space="preserve">
@@ -539,7 +539,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi premium con allegati]</t>
+      <t>[Solo per messaggi con allegati]</t>
     </r>
     <r>
       <rPr>
@@ -1214,6 +1214,9 @@
     <t>-</t>
   </si>
   <si>
+    <t>Scarica il documento</t>
+  </si>
+  <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
@@ -1234,7 +1237,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1329,18 +1332,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
 </sst>
 </file>
@@ -2143,7 +2134,7 @@
         <v>97</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" s="34" t="s">
         <v>97</v>
@@ -2152,10 +2143,10 @@
         <v>96</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J6" s="34" t="s">
         <v>97</v>
@@ -2175,7 +2166,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>63</v>
@@ -2219,7 +2210,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>97</v>
@@ -2231,7 +2222,7 @@
         <v>97</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="34" t="s">
         <v>97</v>
@@ -2263,95 +2254,95 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="H10" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>111</v>
-      </c>
       <c r="M10" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>63</v>
@@ -2363,7 +2354,7 @@
         <v>63</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>63</v>
@@ -2372,10 +2363,10 @@
         <v>63</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="J11" s="34" t="s">
         <v>63</v>
